--- a/analiz-edem/EDEM_MEBEL_vygruzka.xlsx
+++ b/analiz-edem/EDEM_MEBEL_vygruzka.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Все строки Эдем" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="По помещениям" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Сверка с ВОР" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Что проверить" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Что исправлено" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +567,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Отбор: любое упоминание «Эдем» — серия «Эдем-1» в колонке C «Тип, марка» либо поставщик ООО «Эдем-Мебель» в колонке E.</t>
+          <t>Файл ИСПРАВЛЕННЫЙ: фильтр по «Эдем» в колонке C «Тип, марка» отдаёт всю мебель — 68 строк, 96 шт. Количества с ВОР сходятся по всем 7 позициям.</t>
         </is>
       </c>
     </row>
@@ -796,17 +796,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
@@ -831,24 +831,24 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>3438, 3450, 3466, 3480, 3494, 3508</t>
+          <t>2514, 2608, 3276, 3773, 3851, 3859</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-21.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
@@ -869,11 +869,11 @@
         <v/>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3438, 3450, 3466, 3480, 3494, 3508</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="2">
       <c r="A2" s="13" t="n">
-        <v>2519</v>
+        <v>2514</v>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
@@ -1450,17 +1450,17 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -1490,7 +1490,7 @@
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G3" s="13" t="inlineStr">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="I3" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="14" t="n"/>
       <c r="K3" s="14">
@@ -1544,7 +1544,7 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
-        <v>2542</v>
+        <v>2520</v>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
@@ -1553,22 +1553,22 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>107 Помещение охраны круглосуточного дежурства</t>
+          <t>105.1 Помещение службы безопасности</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
@@ -1598,7 +1598,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
@@ -1612,17 +1612,17 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
@@ -1652,7 +1652,7 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="n">
-        <v>2559</v>
+        <v>2545</v>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>109 - Обработка антисептическими составами Касса для массового катания</t>
+          <t>107 Помещение охраны круглосуточного дежурства</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -1706,7 +1706,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -1760,7 +1760,7 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
-        <v>2571</v>
+        <v>2561</v>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
@@ -1769,22 +1769,22 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>109.1 Помещение кассы</t>
+          <t>109 - Обработка антисептическими составами Касса для массового катания</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -1814,7 +1814,7 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
@@ -1828,17 +1828,17 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -1868,7 +1868,7 @@
     </row>
     <row r="10">
       <c r="A10" s="13" t="n">
-        <v>2580</v>
+        <v>2573</v>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
@@ -1877,22 +1877,22 @@
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>110 Ритейл, помещение для хранения, сушки коньков, выдачи проката и заточки коньков</t>
+          <t>109.1 Помещение кассы</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -1922,7 +1922,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>2612</v>
+        <v>2580</v>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
@@ -1931,22 +1931,22 @@
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>118 Помещение службы безопасности</t>
+          <t>110 Ритейл, помещение для хранения, сушки коньков, выдачи проката и заточки коньков</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
@@ -1976,7 +1976,7 @@
     </row>
     <row r="12">
       <c r="A12" s="13" t="n">
-        <v>2614</v>
+        <v>2608</v>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
@@ -1990,17 +1990,17 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -2030,7 +2030,7 @@
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">
-        <v>2624</v>
+        <v>2612</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>119 Помещение охраны круглосуточного дежурства 2</t>
+          <t>118 Помещение службы безопасности</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="I13" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="14" t="n"/>
       <c r="K13" s="14">
@@ -2084,7 +2084,7 @@
     </row>
     <row r="14">
       <c r="A14" s="13" t="n">
-        <v>2625</v>
+        <v>2614</v>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>119 Помещение охраны круглосуточного дежурства 2</t>
+          <t>118 Помещение службы безопасности</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -2138,7 +2138,7 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="n">
-        <v>2771</v>
+        <v>2624</v>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
@@ -2147,22 +2147,22 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>128 Раздевальная для хоккеистов 1</t>
+          <t>119 Помещение охраны круглосуточного дежурства 2</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -2176,7 +2176,7 @@
         </is>
       </c>
       <c r="I15" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14" t="n"/>
       <c r="K15" s="14">
@@ -2192,7 +2192,7 @@
     </row>
     <row r="16">
       <c r="A16" s="13" t="n">
-        <v>2802</v>
+        <v>2625</v>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
@@ -2201,22 +2201,22 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>129 Раздевальная для хоккеистов 2</t>
+          <t>119 Помещение охраны круглосуточного дежурства 2</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -2246,7 +2246,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13" t="n">
-        <v>2833</v>
+        <v>2771</v>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>130 Раздевальная для хоккеистов 3</t>
+          <t>128 Раздевальная для хоккеистов 1</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="18">
       <c r="A18" s="13" t="n">
-        <v>2864</v>
+        <v>2802</v>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>131 Раздевальная для хоккеистов 4</t>
+          <t>129 Раздевальная для хоккеистов 2</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -2354,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" s="13" t="n">
-        <v>2895</v>
+        <v>2833</v>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>132 Раздевальная для хоккеистов 5</t>
+          <t>130 Раздевальная для хоккеистов 3</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -2408,7 +2408,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13" t="n">
-        <v>2926</v>
+        <v>2864</v>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>133 Раздевальная для хоккеистов 6</t>
+          <t>131 Раздевальная для хоккеистов 4</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -2462,7 +2462,7 @@
     </row>
     <row r="21">
       <c r="A21" s="13" t="n">
-        <v>2984</v>
+        <v>2895</v>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>138 Помещение для работы персонала (место отбора проб)</t>
+          <t>132 Раздевальная для хоккеистов 5</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- мебель»</t>
+          <t>Торговая сеть Россия</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -2515,77 +2515,71 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
-        <v>2985</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>138 Помещение для работы персонала (место отбора проб)</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>м28</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>Gigant GCH-01 (BL)</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>ООО «Эдем- мебель»</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="A22" s="13" t="n">
+        <v>2926</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>133 Раздевальная для хоккеистов 6</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>м17</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="16" t="n">
-        <v>1950</v>
-      </c>
-      <c r="K22" s="16">
+      <c r="I22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14">
         <f>IF(ISNUMBER(J22),I22*J22,0)</f>
         <v/>
       </c>
-      <c r="L22" s="6" t="inlineStr">
-        <is>
-          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
-        </is>
-      </c>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>проценено</t>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n">
-        <v>3247</v>
+        <v>2984</v>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>162.2 Помещение распечатки результатов</t>
+          <t>138 Помещение для работы персонала (место отбора проб)</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -2605,7 +2599,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -2629,66 +2623,72 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="n">
-        <v>3251</v>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>162.2 Помещение распечатки результатов</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>м38</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>Торговая сеть Россия</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="A24" s="6" t="n">
+        <v>2985</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>138 Помещение для работы персонала (место отбора проб)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>м28</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Gigant GCH-01 (BL)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Эдем-Мебель»</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I24" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="14" t="n"/>
-      <c r="K24" s="14">
+      <c r="I24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="K24" s="16">
         <f>IF(ISNUMBER(J24),I24*J24,0)</f>
         <v/>
       </c>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="15" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>проценено</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n">
-        <v>3252</v>
+        <v>3247</v>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -2698,22 +2698,22 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>+ ЭВ*2 Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Торговая сеть Россия</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -2738,31 +2738,31 @@
     </row>
     <row r="26">
       <c r="A26" s="13" t="n">
-        <v>3276</v>
+        <v>3251</v>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>163 Зал универсальный, гимнастики, аэробики ОФП</t>
+          <t>162.2 Помещение распечатки результатов</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-21.0</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="I26" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="14" t="n"/>
       <c r="K26" s="14">
@@ -2792,36 +2792,36 @@
     </row>
     <row r="27">
       <c r="A27" s="13" t="n">
-        <v>3290</v>
+        <v>3252</v>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>165 Хореографический зал</t>
+          <t>162.2 Помещение распечатки результатов</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>Торговая сеть Россия</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -2845,182 +2845,180 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="13" t="n">
+        <v>3276</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>163 Зал универсальный, гимнастики, аэробики ОФП</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14">
+        <f>IF(ISNUMBER(J28),I28*J28,0)</f>
+        <v/>
+      </c>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>3290</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>165 Хореографический зал</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>м17</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>ООО «Эдем-Мебель»</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14">
+        <f>IF(ISNUMBER(J29),I29*J29,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
         <v>3291</v>
       </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>165 Хореографический зал</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>м28</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t>Gigant GCH-01 (BL)</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>ООО «Эдем- Мебель»</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Эдем-Мебель»</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I28" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="16" t="n">
+      <c r="I30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="16" t="n">
         <v>1950</v>
       </c>
-      <c r="K28" s="16">
-        <f>IF(ISNUMBER(J28),I28*J28,0)</f>
-        <v/>
-      </c>
-      <c r="L28" s="6" t="inlineStr">
+      <c r="K30" s="16">
+        <f>IF(ISNUMBER(J30),I30*J30,0)</f>
+        <v/>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
         </is>
       </c>
-      <c r="M28" s="6" t="inlineStr">
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>проценено</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n">
-        <v>3433</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>178 Кабинет главного инженера</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>Кресло компьютерное (с подлокотниками, колеса, газлифт, материал обивки – к/з); 620х620х955-1135(h) мм</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Prestige GTP New</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>ООО «Эдем- Мебель»</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="16" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K29" s="16">
-        <f>IF(ISNUMBER(J29),I29*J29,0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="inlineStr">
-        <is>
-          <t>проценено</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="n">
-        <v>3434</v>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>178 Кабинет главного инженера</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>м17</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>ООО «Эдем- Мебель»</t>
-        </is>
-      </c>
-      <c r="H30" s="13" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I30" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="14">
-        <f>IF(ISNUMBER(J30),I30*J30,0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="13" t="n"/>
-      <c r="M30" s="15" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>3435</v>
+        <v>3433</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -3030,22 +3028,22 @@
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>м28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
+          <t>Кресло компьютерное (с подлокотниками, колеса, газлифт, материал обивки – к/з); 620х620х955-1135(h) мм</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>Gigant GCH-01 (BL)</t>
+          <t>Prestige GTP New</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -3054,20 +3052,16 @@
         </is>
       </c>
       <c r="I31" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J31" s="16" t="n">
-        <v>1950</v>
+        <v>12000</v>
       </c>
       <c r="K31" s="16">
         <f>IF(ISNUMBER(J31),I31*J31,0)</f>
         <v/>
       </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
-        </is>
-      </c>
+      <c r="L31" s="6" t="n"/>
       <c r="M31" s="6" t="inlineStr">
         <is>
           <t>проценено</t>
@@ -3076,11 +3070,11 @@
     </row>
     <row r="32">
       <c r="A32" s="13" t="n">
-        <v>3436</v>
+        <v>3434</v>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -3090,22 +3084,22 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -3129,66 +3123,72 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="n">
-        <v>3437</v>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="A33" s="6" t="n">
+        <v>3435</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>178 Кабинет главного инженера</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>м38</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
-        </is>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>ООО «Эдем- Мебель»</t>
-        </is>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>м28</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>Gigant GCH-01 (BL)</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Эдем-Мебель»</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I33" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="14">
+      <c r="I33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="K33" s="16">
         <f>IF(ISNUMBER(J33),I33*J33,0)</f>
         <v/>
       </c>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="15" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>проценено</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n">
-        <v>3438</v>
+        <v>3436</v>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -3198,22 +3198,22 @@
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -3238,11 +3238,11 @@
     </row>
     <row r="35">
       <c r="A35" s="13" t="n">
-        <v>3439</v>
+        <v>3437</v>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -3252,22 +3252,22 @@
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -3292,36 +3292,36 @@
     </row>
     <row r="36">
       <c r="A36" s="13" t="n">
-        <v>3447</v>
+        <v>3438</v>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>179 Приемная</t>
+          <t>178 Кабинет главного инженера</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Торговая сеть Россия</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -3346,36 +3346,36 @@
     </row>
     <row r="37">
       <c r="A37" s="13" t="n">
-        <v>3448</v>
+        <v>3439</v>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>179 Приемная</t>
+          <t>178 Кабинет главного инженера</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Торговая сеть Россия</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -3400,11 +3400,11 @@
     </row>
     <row r="38">
       <c r="A38" s="13" t="n">
-        <v>3449</v>
+        <v>3447</v>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G38" s="13" t="inlineStr">
@@ -3454,11 +3454,11 @@
     </row>
     <row r="39">
       <c r="A39" s="13" t="n">
-        <v>3450</v>
+        <v>3448</v>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -3468,17 +3468,17 @@
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G39" s="13" t="inlineStr">
@@ -3508,11 +3508,11 @@
     </row>
     <row r="40">
       <c r="A40" s="13" t="n">
-        <v>3451</v>
+        <v>3449</v>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
@@ -3522,17 +3522,17 @@
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
@@ -3562,31 +3562,31 @@
     </row>
     <row r="41">
       <c r="A41" s="13" t="n">
-        <v>3461</v>
+        <v>3450</v>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>180 Кабинет директора с переговорной</t>
+          <t>179 Приемная</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="G41" s="13" t="inlineStr">
@@ -3616,31 +3616,31 @@
     </row>
     <row r="42">
       <c r="A42" s="13" t="n">
-        <v>3464</v>
+        <v>3451</v>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>180 Кабинет директора с переговорной</t>
+          <t>179 Приемная</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="G42" s="13" t="inlineStr">
@@ -3670,11 +3670,11 @@
     </row>
     <row r="43">
       <c r="A43" s="13" t="n">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="I43" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J43" s="14" t="n"/>
       <c r="K43" s="14">
@@ -3724,11 +3724,11 @@
     </row>
     <row r="44">
       <c r="A44" s="13" t="n">
-        <v>3466</v>
+        <v>3464</v>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
@@ -3738,17 +3738,17 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
@@ -3778,11 +3778,11 @@
     </row>
     <row r="45">
       <c r="A45" s="13" t="n">
-        <v>3467</v>
+        <v>3465</v>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -3792,17 +3792,17 @@
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
@@ -3816,7 +3816,7 @@
         </is>
       </c>
       <c r="I45" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J45" s="14" t="n"/>
       <c r="K45" s="14">
@@ -3832,11 +3832,11 @@
     </row>
     <row r="46">
       <c r="A46" s="13" t="n">
-        <v>3468</v>
+        <v>3466</v>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>М84</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>Стол для переговоров прямой; 1800х800х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-24.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
@@ -3886,31 +3886,31 @@
     </row>
     <row r="47">
       <c r="A47" s="13" t="n">
-        <v>3476</v>
+        <v>3467</v>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>181 Кабинет главного бухгалтера</t>
+          <t>180 Кабинет директора с переговорной</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
@@ -3940,31 +3940,31 @@
     </row>
     <row r="48">
       <c r="A48" s="13" t="n">
-        <v>3478</v>
+        <v>3468</v>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>181 Кабинет главного бухгалтера</t>
+          <t>180 Кабинет директора с переговорной</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>М84</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол для переговоров прямой; 1800х800х750(h) мм</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-24.0</t>
         </is>
       </c>
       <c r="G48" s="13" t="inlineStr">
@@ -3994,11 +3994,11 @@
     </row>
     <row r="49">
       <c r="A49" s="13" t="n">
-        <v>3479</v>
+        <v>3476</v>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
@@ -4008,17 +4008,17 @@
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G49" s="13" t="inlineStr">
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="I49" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J49" s="14" t="n"/>
       <c r="K49" s="14">
@@ -4048,11 +4048,11 @@
     </row>
     <row r="50">
       <c r="A50" s="13" t="n">
-        <v>3480</v>
+        <v>3478</v>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
@@ -4062,17 +4062,17 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
@@ -4102,11 +4102,11 @@
     </row>
     <row r="51">
       <c r="A51" s="13" t="n">
-        <v>3481</v>
+        <v>3479</v>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -4116,17 +4116,17 @@
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
@@ -4140,7 +4140,7 @@
         </is>
       </c>
       <c r="I51" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J51" s="14" t="n"/>
       <c r="K51" s="14">
@@ -4156,31 +4156,31 @@
     </row>
     <row r="52">
       <c r="A52" s="13" t="n">
-        <v>3490</v>
+        <v>3480</v>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>182 Помещение главного администратора</t>
+          <t>181 Кабинет главного бухгалтера</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
@@ -4210,31 +4210,31 @@
     </row>
     <row r="53">
       <c r="A53" s="13" t="n">
-        <v>3492</v>
+        <v>3481</v>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>182 Помещение главного администратора</t>
+          <t>181 Кабинет главного бухгалтера</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
@@ -4264,11 +4264,11 @@
     </row>
     <row r="54">
       <c r="A54" s="13" t="n">
-        <v>3493</v>
+        <v>3490</v>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -4278,17 +4278,17 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
@@ -4302,7 +4302,7 @@
         </is>
       </c>
       <c r="I54" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J54" s="14" t="n"/>
       <c r="K54" s="14">
@@ -4318,11 +4318,11 @@
     </row>
     <row r="55">
       <c r="A55" s="13" t="n">
-        <v>3494</v>
+        <v>3492</v>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -4332,17 +4332,17 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
@@ -4372,11 +4372,11 @@
     </row>
     <row r="56">
       <c r="A56" s="13" t="n">
-        <v>3495</v>
+        <v>3493</v>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="I56" s="13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56" s="14" t="n"/>
       <c r="K56" s="14">
@@ -4426,31 +4426,31 @@
     </row>
     <row r="57">
       <c r="A57" s="13" t="n">
-        <v>3504</v>
+        <v>3494</v>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>183 Комната технического персонала</t>
+          <t>182 Помещение главного администратора</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
@@ -4464,7 +4464,7 @@
         </is>
       </c>
       <c r="I57" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J57" s="14" t="n"/>
       <c r="K57" s="14">
@@ -4480,31 +4480,31 @@
     </row>
     <row r="58">
       <c r="A58" s="13" t="n">
-        <v>3506</v>
+        <v>3495</v>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>183 Комната технического персонала</t>
+          <t>182 Помещение главного администратора</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
@@ -4534,11 +4534,11 @@
     </row>
     <row r="59">
       <c r="A59" s="13" t="n">
-        <v>3507</v>
+        <v>3504</v>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
@@ -4588,11 +4588,11 @@
     </row>
     <row r="60">
       <c r="A60" s="13" t="n">
-        <v>3508</v>
+        <v>3506</v>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -4602,17 +4602,17 @@
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
@@ -4642,11 +4642,11 @@
     </row>
     <row r="61">
       <c r="A61" s="13" t="n">
-        <v>3509</v>
+        <v>3507</v>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -4656,17 +4656,17 @@
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -4696,36 +4696,36 @@
     </row>
     <row r="62">
       <c r="A62" s="13" t="n">
-        <v>3517</v>
+        <v>3508</v>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>184 Помещение для трениров</t>
+          <t>183 Комната технического персонала</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>Торговая сеть Россия</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J62" s="14" t="n"/>
       <c r="K62" s="14">
@@ -4749,72 +4749,66 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="6" t="n">
-        <v>3518</v>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>184 Помещение для трениров</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>м28</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>Gigant GCH-01 (BL)</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>ООО «Эдем- Мебель»</t>
-        </is>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
+      <c r="A63" s="13" t="n">
+        <v>3509</v>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>183 Комната технического персонала</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>м83</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I63" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="16" t="n">
-        <v>1950</v>
-      </c>
-      <c r="K63" s="16">
+      <c r="I63" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J63" s="14" t="n"/>
+      <c r="K63" s="14">
         <f>IF(ISNUMBER(J63),I63*J63,0)</f>
         <v/>
       </c>
-      <c r="L63" s="6" t="inlineStr">
-        <is>
-          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
-        </is>
-      </c>
-      <c r="M63" s="6" t="inlineStr">
-        <is>
-          <t>проценено</t>
+      <c r="L63" s="13" t="n"/>
+      <c r="M63" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="n">
-        <v>3522</v>
+        <v>3517</v>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -4824,22 +4818,22 @@
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -4863,91 +4857,97 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="n">
-        <v>3523</v>
-      </c>
-      <c r="B65" s="13" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="A65" s="6" t="n">
+        <v>3518</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>184 Помещение для трениров</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
-        <is>
-          <t>м38</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
-        </is>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>Торговая сеть Россия</t>
-        </is>
-      </c>
-      <c r="H65" s="13" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>м28</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Gigant GCH-01 (BL)</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Эдем-Мебель»</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" s="14" t="n"/>
-      <c r="K65" s="14">
+      <c r="I65" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" s="16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="K65" s="16">
         <f>IF(ISNUMBER(J65),I65*J65,0)</f>
         <v/>
       </c>
-      <c r="L65" s="13" t="n"/>
-      <c r="M65" s="15" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="L65" s="6" t="inlineStr">
+        <is>
+          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>проценено</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="n">
-        <v>3672</v>
+        <v>3522</v>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>187.2 Операторская</t>
+          <t>184 Помещение для трениров</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>ООО «Эдем- Мебель»</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="I66" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J66" s="14" t="n"/>
       <c r="K66" s="14">
@@ -4971,97 +4971,91 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="6" t="n">
-        <v>3673</v>
-      </c>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>187.2 Операторская</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>м28</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
-        </is>
-      </c>
-      <c r="F67" s="6" t="inlineStr">
-        <is>
-          <t>Gigant GCH-01 (BL)</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>ООО «Эдем- Мебель»</t>
-        </is>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="A67" s="13" t="n">
+        <v>3523</v>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>184 Помещение для трениров</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>м38</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="16" t="n">
-        <v>1950</v>
-      </c>
-      <c r="K67" s="16">
+      <c r="I67" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J67" s="14" t="n"/>
+      <c r="K67" s="14">
         <f>IF(ISNUMBER(J67),I67*J67,0)</f>
         <v/>
       </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
-        </is>
-      </c>
-      <c r="M67" s="6" t="inlineStr">
-        <is>
-          <t>проценено</t>
+      <c r="L67" s="13" t="n"/>
+      <c r="M67" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="n">
-        <v>3777</v>
+        <v>3672</v>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>193 Телевизионная комментаторская студия</t>
+          <t>187.2 Операторская</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>Торговая сеть Россия</t>
+          <t>ООО «Эдем-Мебель»</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -5085,86 +5079,92 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="n">
-        <v>3855</v>
-      </c>
-      <c r="B69" s="13" t="inlineStr">
-        <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>199.2 Помещение для фотографа</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="F69" s="13" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>Торговая сеть Россия</t>
-        </is>
-      </c>
-      <c r="H69" s="13" t="inlineStr">
+      <c r="A69" s="6" t="n">
+        <v>3673</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>187.2 Операторская</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>м28</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Gigant GCH-01 (BL)</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Эдем-Мебель»</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
-      <c r="I69" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="14" t="n"/>
-      <c r="K69" s="14">
+      <c r="I69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="16" t="n">
+        <v>1950</v>
+      </c>
+      <c r="K69" s="16">
         <f>IF(ISNUMBER(J69),I69*J69,0)</f>
         <v/>
       </c>
-      <c r="L69" s="13" t="n"/>
-      <c r="M69" s="15" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>цена перенесена сюда из ВОР 02-01-11 (ВОР 8, ВОР 483), сама строка ВОР удалена как дубль</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>проценено</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="n">
-        <v>3863</v>
+        <v>3773</v>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>199.3 Помещение для фотографа</t>
+          <t>193 Телевизионная комментаторская студия</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
@@ -5178,7 +5178,7 @@
         </is>
       </c>
       <c r="I70" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J70" s="14" t="n"/>
       <c r="K70" s="14">
@@ -5193,29 +5193,299 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="A71" s="13" t="n">
+        <v>3777</v>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>193 Телевизионная комментаторская студия</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="14" t="n"/>
+      <c r="K71" s="14">
+        <f>IF(ISNUMBER(J71),I71*J71,0)</f>
+        <v/>
+      </c>
+      <c r="L71" s="13" t="n"/>
+      <c r="M71" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n">
+        <v>3851</v>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>199.2 Помещение для фотографа</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I72" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="14">
+        <f>IF(ISNUMBER(J72),I72*J72,0)</f>
+        <v/>
+      </c>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n">
+        <v>3855</v>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>199.2 Помещение для фотографа</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="14">
+        <f>IF(ISNUMBER(J73),I73*J73,0)</f>
+        <v/>
+      </c>
+      <c r="L73" s="13" t="n"/>
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n">
+        <v>3859</v>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>199.3 Помещение для фотографа</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" s="14" t="n"/>
+      <c r="K74" s="14">
+        <f>IF(ISNUMBER(J74),I74*J74,0)</f>
+        <v/>
+      </c>
+      <c r="L74" s="13" t="n"/>
+      <c r="M74" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n">
+        <v>3863</v>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>199.3 Помещение для фотографа</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>Торговая сеть Россия</t>
+        </is>
+      </c>
+      <c r="H75" s="13" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I75" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="14" t="n"/>
+      <c r="K75" s="14">
+        <f>IF(ISNUMBER(J75),I75*J75,0)</f>
+        <v/>
+      </c>
+      <c r="L75" s="13" t="n"/>
+      <c r="M75" s="15" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="n"/>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
-      <c r="I71" s="9">
-        <f>SUM(I2:I70)</f>
-        <v/>
-      </c>
-      <c r="J71" s="16" t="n"/>
-      <c r="K71" s="17">
-        <f>SUM(K2:K70)</f>
-        <v/>
-      </c>
-      <c r="L71" s="6" t="n"/>
-      <c r="M71" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+      <c r="G76" s="6" t="n"/>
+      <c r="H76" s="6" t="n"/>
+      <c r="I76" s="9">
+        <f>SUM(I2:I75)</f>
+        <v/>
+      </c>
+      <c r="J76" s="16" t="n"/>
+      <c r="K76" s="17">
+        <f>SUM(K2:K75)</f>
+        <v/>
+      </c>
+      <c r="L76" s="6" t="n"/>
+      <c r="M76" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5228,7 +5498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5306,17 +5576,17 @@
       <c r="B3" s="6" t="n"/>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -5337,21 +5607,21 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="20" t="inlineStr">
         <is>
@@ -5364,70 +5634,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H5" s="16">
+        <f>IF(ISNUMBER(G5),F5*G5,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>107 Помещение охраны круглосуточного дежурства</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="16" t="n"/>
-      <c r="H5" s="16" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>м38</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H6" s="16">
-        <f>IF(ISNUMBER(G6),F6*G6,0)</f>
-        <v/>
-      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -5444,70 +5714,70 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H8" s="16">
+        <f>IF(ISNUMBER(G8),F8*G8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>109 - Обработка антисептическими составами Касса для массового катания</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H9" s="16">
-        <f>IF(ISNUMBER(G9),F9*G9,0)</f>
-        <v/>
-      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -5524,70 +5794,70 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>м38</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H11" s="16">
+        <f>IF(ISNUMBER(G11),F11*G11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>109.1 Помещение кассы</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="16" t="n"/>
-      <c r="H11" s="16" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H12" s="16">
-        <f>IF(ISNUMBER(G12),F12*G12,0)</f>
-        <v/>
-      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -5604,119 +5874,119 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>м38</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H14" s="16">
+        <f>IF(ISNUMBER(G14),F14*G14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>110 Ритейл, помещение для хранения, сушки коньков, выдачи проката и заточки коньков</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="16" t="n"/>
+      <c r="H15" s="16" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>м17</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H15" s="16">
-        <f>IF(ISNUMBER(G15),F15*G15,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="F16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H16" s="16">
+        <f>IF(ISNUMBER(G16),F16*G16,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>118 Помещение службы безопасности</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="16" t="n"/>
-      <c r="H16" s="16" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>м38</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H17" s="16">
-        <f>IF(ISNUMBER(G17),F17*G17,0)</f>
-        <v/>
-      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
@@ -5733,43 +6003,56 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>119 Помещение охраны круглосуточного дежурства 2</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="16" t="n"/>
-      <c r="H19" s="16" t="n"/>
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>м38</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H19" s="16">
+        <f>IF(ISNUMBER(G19),F19*G19,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
@@ -5782,70 +6065,70 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H21" s="16">
-        <f>IF(ISNUMBER(G21),F21*G21,0)</f>
-        <v/>
-      </c>
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>119 Помещение охраны круглосуточного дежурства 2</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="16" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>128 Раздевальная для хоккеистов 1</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="16" t="n"/>
-      <c r="H22" s="16" t="n"/>
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>м38</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H22" s="16">
+        <f>IF(ISNUMBER(G22),F22*G22,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F23" s="6" t="n">
@@ -5864,7 +6147,7 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>129 Раздевальная для хоккеистов 2</t>
+          <t>128 Раздевальная для хоккеистов 1</t>
         </is>
       </c>
       <c r="B24" s="19" t="inlineStr">
@@ -5913,7 +6196,7 @@
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>130 Раздевальная для хоккеистов 3</t>
+          <t>129 Раздевальная для хоккеистов 2</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
@@ -5962,7 +6245,7 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>131 Раздевальная для хоккеистов 4</t>
+          <t>130 Раздевальная для хоккеистов 3</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
@@ -6011,7 +6294,7 @@
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>132 Раздевальная для хоккеистов 5</t>
+          <t>131 Раздевальная для хоккеистов 4</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -6060,7 +6343,7 @@
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>133 Раздевальная для хоккеистов 6</t>
+          <t>132 Раздевальная для хоккеистов 5</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -6109,7 +6392,7 @@
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>138 Помещение для работы персонала (место отбора проб)</t>
+          <t>133 Раздевальная для хоккеистов 6</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -6156,77 +6439,77 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>м28</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>Gigant GCH-01 (BL)</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="16" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H36" s="16">
-        <f>IF(ISNUMBER(G36),F36*G36,0)</f>
-        <v/>
-      </c>
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>138 Помещение для работы персонала (место отбора проб)</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="16" t="n"/>
+      <c r="H36" s="16" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>162.2 Помещение распечатки результатов</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="16" t="n"/>
-      <c r="H37" s="16" t="n"/>
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>м17</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H37" s="16">
+        <f>IF(ISNUMBER(G37),F37*G37,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м28</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Gigant GCH-01 (BL)</t>
         </is>
       </c>
       <c r="F38" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
+      <c r="G38" s="16" t="n">
+        <v>1950</v>
       </c>
       <c r="H38" s="16">
         <f>IF(ISNUMBER(G38),F38*G38,0)</f>
@@ -6234,52 +6517,39 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>м38</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H39" s="16">
-        <f>IF(ISNUMBER(G39),F39*G39,0)</f>
-        <v/>
-      </c>
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>162.2 Помещение распечатки результатов</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="16" t="n"/>
+      <c r="H39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>+ ЭВ*2 Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F40" s="6" t="n">
@@ -6296,39 +6566,52 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
-        <is>
-          <t>163 Зал универсальный, гимнастики, аэробики ОФП</t>
-        </is>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="16" t="n"/>
-      <c r="H41" s="16" t="n"/>
+      <c r="A41" s="6" t="n"/>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>м38</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H41" s="16">
+        <f>IF(ISNUMBER(G41),F41*G41,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="6" t="n"/>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-21.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F42" s="6" t="n">
@@ -6347,12 +6630,12 @@
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>165 Хореографический зал</t>
+          <t>163 Зал универсальный, гимнастики, аэробики ОФП</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
         <is>
-          <t>148.2 ЭК 2</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C43" s="6" t="n"/>
@@ -6367,17 +6650,17 @@
       <c r="B44" s="6" t="n"/>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="F44" s="6" t="n">
@@ -6394,75 +6677,77 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>м28</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Gigant GCH-01 (BL)</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="16" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H45" s="16">
-        <f>IF(ISNUMBER(G45),F45*G45,0)</f>
-        <v/>
-      </c>
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>165 Хореографический зал</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="16" t="n"/>
+      <c r="H45" s="16" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>178 Кабинет главного инженера</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="16" t="n"/>
-      <c r="H46" s="16" t="n"/>
+      <c r="A46" s="6" t="n"/>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>м17</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H46" s="16">
+        <f>IF(ISNUMBER(G46),F46*G46,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n"/>
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>м28</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Кресло компьютерное (с подлокотниками, колеса, газлифт, материал обивки – к/з); 620х620х955-1135(h) мм</t>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Prestige GTP New</t>
+          <t>Gigant GCH-01 (BL)</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="16" t="n">
-        <v>12000</v>
+        <v>1950</v>
       </c>
       <c r="H47" s="16">
         <f>IF(ISNUMBER(G47),F47*G47,0)</f>
@@ -6470,59 +6755,46 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="n"/>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>м17</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
-        </is>
-      </c>
-      <c r="F48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H48" s="16">
-        <f>IF(ISNUMBER(G48),F48*G48,0)</f>
-        <v/>
-      </c>
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>178 Кабинет главного инженера</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="16" t="n"/>
+      <c r="H48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n"/>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>м28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
+          <t>Кресло компьютерное (с подлокотниками, колеса, газлифт, материал обивки – к/з); 620х620х955-1135(h) мм</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Gigant GCH-01 (BL)</t>
+          <t>Prestige GTP New</t>
         </is>
       </c>
       <c r="F49" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>1950</v>
+        <v>12000</v>
       </c>
       <c r="H49" s="16">
         <f>IF(ISNUMBER(G49),F49*G49,0)</f>
@@ -6534,17 +6806,17 @@
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F50" s="6" t="n">
@@ -6565,26 +6837,24 @@
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м28</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Gigant GCH-01 (BL)</t>
         </is>
       </c>
       <c r="F51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>1950</v>
       </c>
       <c r="H51" s="16">
         <f>IF(ISNUMBER(G51),F51*G51,0)</f>
@@ -6596,17 +6866,17 @@
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F52" s="6" t="n">
@@ -6627,17 +6897,17 @@
       <c r="B53" s="6" t="n"/>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F53" s="6" t="n">
@@ -6654,39 +6924,52 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
-        <is>
-          <t>179 Приемная</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="6" t="n"/>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="16" t="n"/>
+      <c r="A54" s="6" t="n"/>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>м39</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H54" s="16">
+        <f>IF(ISNUMBER(G54),F54*G54,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n"/>
       <c r="B55" s="6" t="n"/>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="F55" s="6" t="n">
@@ -6703,52 +6986,39 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="6" t="n"/>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H56" s="16">
-        <f>IF(ISNUMBER(G56),F56*G56,0)</f>
-        <v/>
-      </c>
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>179 Приемная</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+      <c r="G56" s="16" t="n"/>
+      <c r="H56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n"/>
       <c r="B57" s="6" t="n"/>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
@@ -6769,17 +7039,17 @@
       <c r="B58" s="6" t="n"/>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F58" s="6" t="n">
@@ -6800,17 +7070,17 @@
       <c r="B59" s="6" t="n"/>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
@@ -6827,39 +7097,52 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
-        <is>
-          <t>180 Кабинет директора с переговорной</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="6" t="n"/>
-      <c r="G60" s="16" t="n"/>
-      <c r="H60" s="16" t="n"/>
+      <c r="A60" s="6" t="n"/>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>м39</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H60" s="16">
+        <f>IF(ISNUMBER(G60),F60*G60,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="n"/>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="F61" s="6" t="n">
@@ -6876,56 +7159,43 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="6" t="n"/>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H62" s="16">
-        <f>IF(ISNUMBER(G62),F62*G62,0)</f>
-        <v/>
-      </c>
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>180 Кабинет директора с переговорной</t>
+        </is>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+      <c r="G62" s="16" t="n"/>
+      <c r="H62" s="16" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6" t="n"/>
       <c r="B63" s="6" t="n"/>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F63" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G63" s="20" t="inlineStr">
         <is>
@@ -6942,17 +7212,17 @@
       <c r="B64" s="6" t="n"/>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F64" s="6" t="n">
@@ -6973,21 +7243,21 @@
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G65" s="20" t="inlineStr">
         <is>
@@ -7004,17 +7274,17 @@
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>М84</t>
+          <t>м39</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Стол для переговоров прямой; 1800х800х750(h) мм</t>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-24.0</t>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
         </is>
       </c>
       <c r="F66" s="6" t="n">
@@ -7031,39 +7301,52 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
-        <is>
-          <t>181 Кабинет главного бухгалтера</t>
-        </is>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="16" t="n"/>
-      <c r="H67" s="16" t="n"/>
+      <c r="A67" s="6" t="n"/>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>м83</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H67" s="16">
+        <f>IF(ISNUMBER(G67),F67*G67,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
       <c r="B68" s="6" t="n"/>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>М84</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Стол для переговоров прямой; 1800х800х750(h) мм</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-24.0</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
@@ -7080,56 +7363,43 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H69" s="16">
-        <f>IF(ISNUMBER(G69),F69*G69,0)</f>
-        <v/>
-      </c>
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>181 Кабинет главного бухгалтера</t>
+        </is>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+      <c r="G69" s="16" t="n"/>
+      <c r="H69" s="16" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="n"/>
       <c r="B70" s="6" t="n"/>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F70" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G70" s="20" t="inlineStr">
         <is>
@@ -7146,17 +7416,17 @@
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F71" s="6" t="n">
@@ -7177,21 +7447,21 @@
       <c r="B72" s="6" t="n"/>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F72" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G72" s="20" t="inlineStr">
         <is>
@@ -7204,39 +7474,52 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
-        <is>
-          <t>182 Помещение главного администратора</t>
-        </is>
-      </c>
-      <c r="B73" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
-      <c r="G73" s="16" t="n"/>
-      <c r="H73" s="16" t="n"/>
+      <c r="A73" s="6" t="n"/>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>м39</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H73" s="16">
+        <f>IF(ISNUMBER(G73),F73*G73,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="n"/>
       <c r="B74" s="6" t="n"/>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="F74" s="6" t="n">
@@ -7253,56 +7536,43 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="6" t="n"/>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H75" s="16">
-        <f>IF(ISNUMBER(G75),F75*G75,0)</f>
-        <v/>
-      </c>
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>182 Помещение главного администратора</t>
+        </is>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n"/>
+      <c r="F75" s="6" t="n"/>
+      <c r="G75" s="16" t="n"/>
+      <c r="H75" s="16" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G76" s="20" t="inlineStr">
         <is>
@@ -7319,17 +7589,17 @@
       <c r="B77" s="6" t="n"/>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F77" s="6" t="n">
@@ -7350,21 +7620,21 @@
       <c r="B78" s="6" t="n"/>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F78" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G78" s="20" t="inlineStr">
         <is>
@@ -7377,43 +7647,56 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="inlineStr">
-        <is>
-          <t>183 Комната технического персонала</t>
-        </is>
-      </c>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="n"/>
-      <c r="D79" s="6" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="6" t="n"/>
-      <c r="G79" s="16" t="n"/>
-      <c r="H79" s="16" t="n"/>
+      <c r="A79" s="6" t="n"/>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>м39</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H79" s="16">
+        <f>IF(ISNUMBER(G79),F79*G79,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="6" t="n"/>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="F80" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G80" s="20" t="inlineStr">
         <is>
@@ -7426,52 +7709,39 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="6" t="n"/>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F81" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H81" s="16">
-        <f>IF(ISNUMBER(G81),F81*G81,0)</f>
-        <v/>
-      </c>
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>183 Комната технического персонала</t>
+        </is>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n"/>
+      <c r="F81" s="6" t="n"/>
+      <c r="G81" s="16" t="n"/>
+      <c r="H81" s="16" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="n"/>
       <c r="B82" s="6" t="n"/>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F82" s="6" t="n">
@@ -7492,17 +7762,17 @@
       <c r="B83" s="6" t="n"/>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>м39</t>
+          <t>м33</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-46.0</t>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
         </is>
       </c>
       <c r="F83" s="6" t="n">
@@ -7523,17 +7793,17 @@
       <c r="B84" s="6" t="n"/>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F84" s="6" t="n">
@@ -7550,43 +7820,56 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
-        <is>
-          <t>184 Помещение для трениров</t>
-        </is>
-      </c>
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t>148.2 ЭК 2</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="16" t="n"/>
-      <c r="H85" s="16" t="n"/>
+      <c r="A85" s="6" t="n"/>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>м39</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Шкаф двухстворчатый для одежды (2 распашные двери, перекладина); 768х403х1945(h) мм</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-46.0</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H85" s="16">
+        <f>IF(ISNUMBER(G85),F85*G85,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="n"/>
       <c r="B86" s="6" t="n"/>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м83</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
         </is>
       </c>
       <c r="F86" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G86" s="20" t="inlineStr">
         <is>
@@ -7599,50 +7882,39 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="6" t="n"/>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>м28</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>Gigant GCH-01 (BL)</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G87" s="16" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H87" s="16">
-        <f>IF(ISNUMBER(G87),F87*G87,0)</f>
-        <v/>
-      </c>
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>184 Помещение для трениров</t>
+        </is>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+      <c r="E87" s="6" t="n"/>
+      <c r="F87" s="6" t="n"/>
+      <c r="G87" s="16" t="n"/>
+      <c r="H87" s="16" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="n"/>
       <c r="B88" s="6" t="n"/>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>м83</t>
+          <t>м17</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
         </is>
       </c>
       <c r="F88" s="6" t="n">
@@ -7663,26 +7935,24 @@
       <c r="B89" s="6" t="n"/>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>м38</t>
+          <t>м28</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
+          <t>Gigant GCH-01 (BL)</t>
         </is>
       </c>
       <c r="F89" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G89" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>1950</v>
       </c>
       <c r="H89" s="16">
         <f>IF(ISNUMBER(G89),F89*G89,0)</f>
@@ -7690,43 +7960,56 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="inlineStr">
-        <is>
-          <t>187.2 Операторская</t>
-        </is>
-      </c>
-      <c r="B90" s="19" t="inlineStr">
-        <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="16" t="n"/>
-      <c r="H90" s="16" t="n"/>
+      <c r="A90" s="6" t="n"/>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>м83</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Тумба выкатная с центральным замком (3 выдвижных ящика, колеса); 397х500х610(h) мм</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-37.0 ц/з</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G90" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H90" s="16">
+        <f>IF(ISNUMBER(G90),F90*G90,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="n"/>
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>м17</t>
+          <t>м38</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+          <t>Шкаф двухстворчатый высокий со стеклом комбинированный (4 распашные двери, 2 верхние двери – стекло, 3 полки); 768х403х1945(h) мм</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-22.0</t>
+          <t>Серия «Эдем-1», арт.Э-44.0 + 47.0*2 + 80.0*2 + ЭВ*2</t>
         </is>
       </c>
       <c r="F91" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G91" s="20" t="inlineStr">
         <is>
@@ -7739,77 +8022,77 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>м28</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>Gigant GCH-01 (BL)</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="16" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H92" s="16">
-        <f>IF(ISNUMBER(G92),F92*G92,0)</f>
-        <v/>
-      </c>
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>187.2 Операторская</t>
+        </is>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="16" t="n"/>
+      <c r="H92" s="16" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="18" t="inlineStr">
-        <is>
-          <t>193 Телевизионная комментаторская студия</t>
-        </is>
-      </c>
-      <c r="B93" s="19" t="inlineStr">
-        <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="n"/>
-      <c r="D93" s="6" t="n"/>
-      <c r="E93" s="6" t="n"/>
-      <c r="F93" s="6" t="n"/>
-      <c r="G93" s="16" t="n"/>
-      <c r="H93" s="16" t="n"/>
+      <c r="A93" s="6" t="n"/>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>м17</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1400х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-22.0</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H93" s="16">
+        <f>IF(ISNUMBER(G93),F93*G93,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="n"/>
       <c r="B94" s="6" t="n"/>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>м28</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стул для посетителей (материал обивки – к/з); 540х440х820(h) мм</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Gigant GCH-01 (BL)</t>
         </is>
       </c>
       <c r="F94" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G94" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
+      <c r="G94" s="16" t="n">
+        <v>1950</v>
       </c>
       <c r="H94" s="16">
         <f>IF(ISNUMBER(G94),F94*G94,0)</f>
@@ -7819,12 +8102,12 @@
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>199.2 Помещение для фотографа</t>
+          <t>193 Телевизионная комментаторская студия</t>
         </is>
       </c>
       <c r="B95" s="19" t="inlineStr">
         <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
         </is>
       </c>
       <c r="C95" s="6" t="n"/>
@@ -7839,21 +8122,21 @@
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>м33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
         </is>
       </c>
       <c r="F96" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G96" s="20" t="inlineStr">
         <is>
@@ -7866,71 +8149,213 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="18" t="inlineStr">
-        <is>
-          <t>199.3 Помещение для фотографа</t>
-        </is>
-      </c>
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>ПОМЕЩЕНИЯ КАФЕ</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="16" t="n"/>
-      <c r="H97" s="16" t="n"/>
+      <c r="A97" s="6" t="n"/>
+      <c r="B97" s="6" t="n"/>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H97" s="16">
+        <f>IF(ISNUMBER(G97),F97*G97,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>м33</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>Серия «Эдем-1», арт.Э-26.7</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="20" t="inlineStr">
-        <is>
-          <t>ЦЕНЫ НЕТ</t>
-        </is>
-      </c>
-      <c r="H98" s="16">
-        <f>IF(ISNUMBER(G98),F98*G98,0)</f>
-        <v/>
-      </c>
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>199.2 Помещение для фотографа</t>
+        </is>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+      <c r="E98" s="6" t="n"/>
+      <c r="F98" s="6" t="n"/>
+      <c r="G98" s="16" t="n"/>
+      <c r="H98" s="16" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="n"/>
       <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="9" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H99" s="16">
+        <f>IF(ISNUMBER(G99),F99*G99,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="n"/>
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H100" s="16">
+        <f>IF(ISNUMBER(G100),F100*G100,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>199.3 Помещение для фотографа</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>ТХ.2. ОБОРУДОВАНИЕ, МЕБЕЛЬ И ИНВЕНТАРЬ ПО ПОМЕЩЕНИЯМ (03-01/07.21П-ТХ.2.СО)</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+      <c r="G101" s="16" t="n"/>
+      <c r="H101" s="16" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="n"/>
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-21.0</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H102" s="16">
+        <f>IF(ISNUMBER(G102),F102*G102,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>м33</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Тумба для оргтехники двухстворчатая (2 распашные двери, ниша); 800х550х610(h) мм</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Серия «Эдем-1», арт.Э-26.7</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="20" t="inlineStr">
+        <is>
+          <t>ЦЕНЫ НЕТ</t>
+        </is>
+      </c>
+      <c r="H103" s="16">
+        <f>IF(ISNUMBER(G103),F103*G103,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="9">
-        <f>SUM(F2:F98)</f>
-        <v/>
-      </c>
-      <c r="G99" s="16" t="n"/>
-      <c r="H99" s="17">
-        <f>SUM(H2:H98)</f>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="9">
+        <f>SUM(F2:F103)</f>
+        <v/>
+      </c>
+      <c r="G104" s="16" t="n"/>
+      <c r="H104" s="17">
+        <f>SUM(H2:H103)</f>
         <v/>
       </c>
     </row>
@@ -8031,31 +8456,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Стол рабочий прямой; 1200х700х750 (h) мм</t>
-        </is>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="D5" s="22" t="n">
+      <c r="C5" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="22" t="n">
+      <c r="D5" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="22" t="inlineStr">
-        <is>
-          <t>ВОР больше СО на 1</t>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>сходится (объединены два написания одного наименования)</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8512,7 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>Стол рабочий прямой; 1200х700х750(h) мм</t>
+          <t>(объединено) Стол рабочий прямой; 1200х700х750(h) мм</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
@@ -8096,16 +8521,20 @@
         </is>
       </c>
       <c r="C7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="19" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" s="19" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>нет прямой пары в ВОРе; близкая строка ВОРа отнесена к «Стол рабочий прямой; 1200х700х750 (h) мм» — проверить</t>
+          <t>объединено со строкой выше — два написания одного наименования</t>
         </is>
       </c>
     </row>
@@ -8352,11 +8781,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="86" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
@@ -8364,7 +8793,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ЭДЕМ-МЕБЕЛЬ — ЗАМЕЧАНИЯ К ПРОВЕРКЕ</t>
+          <t>ЭДЕМ-МЕБЕЛЬ — ЧТО ИСПРАВЛЕНО И ЧТО ОСТАЛОСЬ</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8805,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Замечание</t>
+          <t>Что сделано / что осталось</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -8386,51 +8815,51 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Влияние</t>
+          <t>Результат</t>
         </is>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>Вся мебель серии «Эдем-1» идёт без цены: 63 строки, 87 шт, колонка H пустая → сумма 0 руб. Это единственная крупная непроценённая группа в разделе ТХ.2.</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>Спецификация, строки 2519–3863; лист «Свод», блок А</t>
-        </is>
-      </c>
-      <c r="D4" s="22" t="inlineStr">
-        <is>
-          <t>Стоимость раздела ТХ.2 занижена на всю мебель «Эдем-1»</t>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО. Файл был сохранён с включённым фильтром по колонке B «Наименование» (3 значения) — скрыто 4311 строк из 4705. Именно поэтому поиск по «Эдем» отдавал не всё. Фильтр снят, все строки показаны.</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>Спецификация, автофильтр A1:K4339</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Фильтр по «Эдем» теперь видит весь лист</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Поставщик написан в двух вариантах: «ООО «Эдем- мебель»» (2 строки) и «ООО «Эдем- Мебель»» (15 строк). Плюс лишний пробел после дефиса в обоих вариантах.</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>Спецификация, колонка E, строки 2984, 2985 vs остальные 15</t>
-        </is>
-      </c>
-      <c r="D5" s="22" t="inlineStr">
-        <is>
-          <t>Ломается группировка/сводные по поставщику</t>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО. Пять строк стола 1200х700х750 (стр. 2514, 2608, 3773, 3851, 3859) шли с пустой колонкой C и с лишним пробелом в наименовании — фильтр по «Эдем» их не находил. Наименование приведено к единому виду, проставлен арт.Э-21.0.</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Спецификация, колонка B и C</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>В фильтр вернулись 9 шт</t>
         </is>
       </c>
     </row>
@@ -8442,127 +8871,171 @@
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
-          <t>Одни и те же позиции «Эдем-1» в разных помещениях имеют разного поставщика: где-то «ООО «Эдем-Мебель»», где-то обезличенное «Торговая сеть Россия» (52 строки из 63).</t>
+          <t>ИСПРАВЛЕНО. Стр.3252: из артикула убран мусорный префикс «+ ЭВ*2», приклеившийся от соседней строки 3251.</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>Спецификация, колонка E; лист «Все строки Эдем»</t>
+          <t>Спецификация, стр.3252, колонка C</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Непонятно, кто реально поставляет мебель; риск двойного счёта</t>
+          <t>Артикул стал единообразным</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>У поставщика «ООО «Эдем-Мебель»» проценены только не-эдемовские позиции: стул Gigant GCH-01 (BL) — 1950 руб. и кресло Prestige GTP New — 12 000 руб. Итого 29 550 руб. Сама мебель «Эдем-1» у этого же поставщика — без цены.</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>Спецификация, строки 2985, 3291, 3433, 3435, 3518, 3673</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>Цена есть только на 10 шт из 97</t>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО. Поставщик приведён к единому написанию «ООО «Эдем-Мебель»» в 17 строках — было «ООО «Эдем- мебель»» ×2 и «ООО «Эдем- Мебель»» ×15, в обоих лишний пробел после дефиса.</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Спецификация, колонка E</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Группировка по поставщику работает</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>Два варианта написания одного наименования: «Стол рабочий прямой; 1200х700х750 (h) мм» (5 строк, 9 шт, без артикула) и «Стол рабочий прямой; 1200х700х750(h) мм» (1 строка, 1 шт, арт. Э-21.0). Лист «Сверка ТХ.2» отдельно помечает: «нет прямой пары в ВОРе — проверить».</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>Спецификация, строка 3276 и строки без артикула; лист «Сверка ТХ.2»</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>Позиция может не сойтись с ВОР / задвоиться</t>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО. Разрыв внутри слова: «Торгов ая сеть Россия» → «Торговая сеть Россия», 13 строк.</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Спецификация, колонка E</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Фильтр по поставщику не двоится</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Строка 3252: артикул записан как «+ ЭВ*2 Серия «Эдем-1», арт.Э-26.7» — обрывок от соседней позиции приклеился в начало.</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>Спецификация, строка 3252, колонка C</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>Мусор в артикуле, не найдётся поиском</t>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>СВЕРКА СОШЛАСЬ. После объединения двух написаний стола 1200 количество по СО = 10 шт = количество по ВОР = 10 шт. Расхождение «ВОР больше СО на 1» было артефактом орфографии. По всем 7 позициям «Эдем-1»: 28/28, 23/23, 16/16, 12/12, 10/10, 6/6, 1/1 — расхождений нет.</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Лист «Сверка с ВОР»</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Объёмы подтверждены, править не нужно</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>Количества по всем позициям «Эдем-1» с ВОР сходятся: м38 28/28, м17 23/23, м33 16/16, м83 12/12, м39 6/6, М84 1/1. Расхождений нет — вопрос только в цене.</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>Лист «Сверка с ВОР»</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>Подтверждено: править нужно цены, не объёмы</t>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>ОСТАЛОСЬ. Мебель «Эдем-1» по-прежнему без цены: 68 строк, 96 шт, колонка H пустая, сумма 0 руб. Проценены только не-эдемовские позиции у этого поставщика — стул Gigant (1950 руб.) и кресло Prestige (12 000 руб.), итого 29 550 руб.</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Спецификация, колонка H</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Стоимость раздела ТХ.2 занижена на всю мебель</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>На листе «Правки» по всем 69 строкам «Эдем» зафиксировано 52 правки, и все — только приведение «Шт.»/«шт» к «шт.». Цены никто не трогал.</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>Лист «Правки» книги-источника</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>История правок подтверждает: цены не заводились</t>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>ОСТАЛОСЬ, НУЖНО РЕШЕНИЕ. В 52 строках из 68 поставщиком указано обезличенное «Торговая сеть Россия», а не «ООО «Эдем-Мебель»» — при том, что позиции те же. Это не орфография, а вопрос к договору: менять не стал.</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Спецификация, колонка E</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>Непонятно, кто реально поставляет</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>ПОД ВОПРОСОМ. «Стол рабочий прямой; 1600х700х750(h) мм» (поз. м221, 5 строк, 7 шт) — та же офисная линейка, но артикул не проставлен нигде в файле. Признаков «Эдема» нет, поэтому не трогал. Если это тоже Эдем — нужен артикул.</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Спецификация, стр. 2535, 2556, 2568, 2620 и др.</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>7 шт вне фильтра по «Эдем»</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>ПОД ВОПРОСОМ, вне Эдема. Поставщик «Электротехника и Авто- матика» (5 строк) — разрыв внутри слова, но канонического написания в файле нет, поэтому не исправлял.</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>Спецификация, колонка E</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>Мелкий мусор в справочнике поставщиков</t>
         </is>
       </c>
     </row>
